--- a/order_forms/045_virtual_event_service_order_form--order_forms.xlsx
+++ b/order_forms/045_virtual_event_service_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Event Details</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>service_orders</t>
+          <t>event_service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service Orders</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -570,41 +570,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>attendee_info</t>
+          <t>event_participants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Attendee Info</t>
+          <t>Participants</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>event_date_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Event Details</t>
+          <t>Event Date and Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,19 +616,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>service_orders</t>
+          <t>event_services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Service Orders</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Select multiple options</t>
-        </is>
-      </c>
+          <t>Additional Services</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -643,18 +639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attendee_info</t>
+          <t>event_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Attendee Info</t>
+          <t>Event Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,66 +662,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>attendee_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event Details</t>
+          <t>Attendee Information</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>service_orders</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Service Orders</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Select one option</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>attendee_info</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Attendee Info</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -742,12 +688,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -770,153 +716,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>service_orders_choices</t>
+          <t>event_service_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>service_orders_choices</t>
+          <t>event_service_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>service_orders_choices</t>
+          <t>event_service_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service_orders_choices</t>
+          <t>event_services_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service_orders_choices</t>
+          <t>event_services_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_orders_choices</t>
+          <t>event_services_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>service_orders_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>service_orders_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>service_orders_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
